--- a/data/trans_dic/P1804_2016_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1804_2016_2023-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,48</t>
+          <t>3,07; 6,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,91</t>
+          <t>2,18; 6,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,79</t>
+          <t>5,05; 8,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,39</t>
+          <t>4,7; 8,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,81</t>
+          <t>4,48; 6,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,28</t>
+          <t>3,92; 6,55</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,22</t>
+          <t>4,34; 7,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,33</t>
+          <t>6,52; 10,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 10,67</t>
+          <t>6,93; 10,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 10,41</t>
+          <t>7,38; 10,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,31</t>
+          <t>6,15; 8,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,69</t>
+          <t>7,5; 10,05</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,06</t>
+          <t>3,82; 7,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,16</t>
+          <t>2,08; 4,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 14,1</t>
+          <t>9,42; 13,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,94</t>
+          <t>4,84; 8,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,18</t>
+          <t>7,1; 10,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,63</t>
+          <t>3,71; 5,7</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,94</t>
+          <t>7,37; 11,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,31</t>
+          <t>6,67; 10,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 14,55</t>
+          <t>9,99; 14,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,15</t>
+          <t>9,78; 13,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 12,24</t>
+          <t>9,27; 12,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,67</t>
+          <t>8,63; 10,93</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,26</t>
+          <t>5,44; 7,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,56</t>
+          <t>5,35; 7,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 11,05</t>
+          <t>8,83; 10,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,63</t>
+          <t>7,67; 9,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,86</t>
+          <t>7,43; 8,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,3</t>
+          <t>6,76; 8,05</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64748</t>
+          <t>72285</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20565; 43694</t>
+          <t>20721; 42180</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13555; 37586</t>
+          <t>15086; 42011</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31666; 59110</t>
+          <t>34001; 58921</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32276; 56676</t>
+          <t>34402; 62245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57907; 91757</t>
+          <t>60387; 93616</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49138; 82345</t>
+          <t>55791; 93159</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>71399</t>
+          <t>88990</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83205</t>
+          <t>95341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>154604</t>
+          <t>184330</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44882; 73811</t>
+          <t>44375; 74180</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35415; 99349</t>
+          <t>68423; 114240</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73680; 111231</t>
+          <t>72302; 110627</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67816; 99760</t>
+          <t>79030; 115643</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>124959; 171575</t>
+          <t>127004; 175755</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>101121; 186853</t>
+          <t>159033; 213031</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>49532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58475</t>
+          <t>73927</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27835; 53598</t>
+          <t>29051; 54843</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12884; 29339</t>
+          <t>16725; 36046</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73777; 110663</t>
+          <t>73917; 109463</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20359; 55249</t>
+          <t>39054; 66019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>111868; 157239</t>
+          <t>109639; 156762</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38033; 75768</t>
+          <t>59696; 91801</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>77281</t>
+          <t>80530</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112455</t>
+          <t>125327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>189736</t>
+          <t>205856</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67634; 102606</t>
+          <t>69128; 103242</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62135; 95555</t>
+          <t>66020; 100495</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105484; 151849</t>
+          <t>104283; 148721</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88595; 132906</t>
+          <t>109417; 146867</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>185006; 242425</t>
+          <t>183607; 244296</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>164731; 215654</t>
+          <t>182058; 230446</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>190834</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>276729</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>467563</t>
+          <t>536400</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>186939; 246481</t>
+          <t>184751; 243225</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>152011; 226927</t>
+          <t>189032; 258774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>322187; 391829</t>
+          <t>312856; 388852</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>228617; 315698</t>
+          <t>286074; 351492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>520169; 614524</t>
+          <t>515476; 615517</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>403907; 519745</t>
+          <t>491092; 584145</t>
         </is>
       </c>
     </row>
